--- a/script/templates/IMPORT_DIPARTIMENTO_E_UOC.xlsx
+++ b/script/templates/IMPORT_DIPARTIMENTO_E_UOC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GZOOM\workspace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GZOOM\workspace\gzoom-legacy\script\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BB34A2-76E5-4E96-8286-B5796D9A9E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D051074C-C615-4131-BA3F-A29716D0D87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="-1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="-1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
   <si>
     <t>UOC Code</t>
   </si>
@@ -62,7 +62,7 @@
     <t>DIP001</t>
   </si>
   <si>
-    <t>Dipartimento Test1</t>
+    <t>Dipartimento tecnico/logistico</t>
   </si>
   <si>
     <t>ORG</t>
@@ -77,13 +77,907 @@
     <t/>
   </si>
   <si>
-    <t>UOC001</t>
-  </si>
-  <si>
-    <t>UOC Test1</t>
+    <t>BAA9907</t>
+  </si>
+  <si>
+    <t>GESTIONE RISORSE TECNICHE</t>
   </si>
   <si>
     <t>ORGANIZATION_UNIT</t>
+  </si>
+  <si>
+    <t>BAA9909</t>
+  </si>
+  <si>
+    <t>GESTIONE SISTEMI INFORMATICI</t>
+  </si>
+  <si>
+    <t>BAA9910</t>
+  </si>
+  <si>
+    <t>INGEGNERIA CLINICA</t>
+  </si>
+  <si>
+    <t>BAA9913</t>
+  </si>
+  <si>
+    <t>INVESTIMENTI E ENERGY MANAGEMENT</t>
+  </si>
+  <si>
+    <t>BAA9906</t>
+  </si>
+  <si>
+    <t>PROVVEDITORATO ED ECONOMATO</t>
+  </si>
+  <si>
+    <t>DIP002</t>
+  </si>
+  <si>
+    <t>Dipartimento dell'emergenza e dell'area critica</t>
+  </si>
+  <si>
+    <t>BSEA2200</t>
+  </si>
+  <si>
+    <t>CHIRURGIA D'URGENZA</t>
+  </si>
+  <si>
+    <t>BSEA2200C</t>
+  </si>
+  <si>
+    <t>CHIRURGIA D'URGENZA C.O.</t>
+  </si>
+  <si>
+    <t>BSEA1000</t>
+  </si>
+  <si>
+    <t>MEDICINA DEA E COMPLESSITA' CLINICA</t>
+  </si>
+  <si>
+    <t>BSEA2500</t>
+  </si>
+  <si>
+    <t>NEUROCHIRURGIA</t>
+  </si>
+  <si>
+    <t>BSEA2500C</t>
+  </si>
+  <si>
+    <t>NEUROCHIRURGIA D'URGENZA C.O.</t>
+  </si>
+  <si>
+    <t>BSEA2202</t>
+  </si>
+  <si>
+    <t>PRONTO SOCCORSO OBI E MEDICINA DI EMERGENZA E URGENZA</t>
+  </si>
+  <si>
+    <t>BSTA4110</t>
+  </si>
+  <si>
+    <t>RADIOLOGIA GENERALE E DI P.S.</t>
+  </si>
+  <si>
+    <t>BSEA1410</t>
+  </si>
+  <si>
+    <t>TRAUMA CENTER UOD</t>
+  </si>
+  <si>
+    <t>DIP003</t>
+  </si>
+  <si>
+    <t>Dipartimento reti tempo-dipendenti</t>
+  </si>
+  <si>
+    <t>BSMP2000</t>
+  </si>
+  <si>
+    <t>CARDIOLOGIA</t>
+  </si>
+  <si>
+    <t>BSEA4820</t>
+  </si>
+  <si>
+    <t>CARDIOLOGIA CON UTIC</t>
+  </si>
+  <si>
+    <t>BSMP2610</t>
+  </si>
+  <si>
+    <t>NEUROFISIOPATOLOGIA</t>
+  </si>
+  <si>
+    <t>BSEA2600</t>
+  </si>
+  <si>
+    <t>NEUROLOGIA</t>
+  </si>
+  <si>
+    <t>BSEA4820-1</t>
+  </si>
+  <si>
+    <t>UTIC EMODINAMICA</t>
+  </si>
+  <si>
+    <t>DIP004</t>
+  </si>
+  <si>
+    <t>Dipartimento integrato oncoematologico e toraco-polmonare</t>
+  </si>
+  <si>
+    <t>BSCS3400</t>
+  </si>
+  <si>
+    <t>CHIRURGIA TORACICA</t>
+  </si>
+  <si>
+    <t>BSOP1900</t>
+  </si>
+  <si>
+    <t>EMATOLOGIA</t>
+  </si>
+  <si>
+    <t>BSOP1911</t>
+  </si>
+  <si>
+    <t>EMATOLOGIA CON TRAPIANTI DI CELLULE STAMINALI EMATOPOIETICHE (CSE) E T.I.</t>
+  </si>
+  <si>
+    <t>BSOP1900-1</t>
+  </si>
+  <si>
+    <t>EMATOLOGIA D.H.</t>
+  </si>
+  <si>
+    <t>BSOP1901</t>
+  </si>
+  <si>
+    <t>MALATTIE RARE DEL GLOBULO ROSSO</t>
+  </si>
+  <si>
+    <t>BSOP3310</t>
+  </si>
+  <si>
+    <t>ONCOLOGIA MEDICA DAY-HOSP</t>
+  </si>
+  <si>
+    <t>BSOP3310-1</t>
+  </si>
+  <si>
+    <t>ONCOLOGIA MEDICA REPARTO</t>
+  </si>
+  <si>
+    <t>BSOP3100</t>
+  </si>
+  <si>
+    <t>PNEUMOLOGIA</t>
+  </si>
+  <si>
+    <t>BSOP4000</t>
+  </si>
+  <si>
+    <t>FISIOPATOLOGIA RESPIRATORIA</t>
+  </si>
+  <si>
+    <t>BSOP3600</t>
+  </si>
+  <si>
+    <t>PNEUMOLOGIA E TERAPIA SEMINTENSIVA RESPIRATORIA</t>
+  </si>
+  <si>
+    <t>BSOP3800</t>
+  </si>
+  <si>
+    <t>SERVIZIO PNEUMOLOGIA INTERVENTISTICA</t>
+  </si>
+  <si>
+    <t>DIP005</t>
+  </si>
+  <si>
+    <t>Dipartimento medico polispecialistico</t>
+  </si>
+  <si>
+    <t>BSMP3000</t>
+  </si>
+  <si>
+    <t>DERMATOLOGIA UOSD</t>
+  </si>
+  <si>
+    <t>BSMP3700</t>
+  </si>
+  <si>
+    <t>DETENUTI UOSD</t>
+  </si>
+  <si>
+    <t>BSMP1401</t>
+  </si>
+  <si>
+    <t>DIABETOLOGIA UOSD</t>
+  </si>
+  <si>
+    <t>BSMP1200</t>
+  </si>
+  <si>
+    <t>ENDOCRINOLOGIA</t>
+  </si>
+  <si>
+    <t>BSTR0811</t>
+  </si>
+  <si>
+    <t>EPATOLOGIA</t>
+  </si>
+  <si>
+    <t>BSTR2010-2</t>
+  </si>
+  <si>
+    <t>GASTROENTEROLOGIA DEGENZA</t>
+  </si>
+  <si>
+    <t>BSTR2010-1</t>
+  </si>
+  <si>
+    <t>GASTROENTEROLOGIA ENDOSCOP.DIGES.URGENZA</t>
+  </si>
+  <si>
+    <t>BSTR2010</t>
+  </si>
+  <si>
+    <t>GASTROENTEROLOGIA ENDOSCOP.DIGESTIVA</t>
+  </si>
+  <si>
+    <t>BSMP1320</t>
+  </si>
+  <si>
+    <t>MEDICINA AD INDIRIZZO GERIATRICO</t>
+  </si>
+  <si>
+    <t>BSMP1100</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 1</t>
+  </si>
+  <si>
+    <t>BSMP1100-2</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 1 - DONNE</t>
+  </si>
+  <si>
+    <t>BSMP1100-1</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 1 - UOMINI</t>
+  </si>
+  <si>
+    <t>BSMP1300</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 2</t>
+  </si>
+  <si>
+    <t>BSMP1300-2</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 2 - DONNE</t>
+  </si>
+  <si>
+    <t>BSMP1300-1</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 2 - UOMINI</t>
+  </si>
+  <si>
+    <t>BSMP0300</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 3</t>
+  </si>
+  <si>
+    <t>BSMP0300-2</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 3 - DONNE</t>
+  </si>
+  <si>
+    <t>BSMP0300-1</t>
+  </si>
+  <si>
+    <t>MEDICINA INTERNA 3 - UOMINI</t>
+  </si>
+  <si>
+    <t>BSMP3020</t>
+  </si>
+  <si>
+    <t>NEFROLOGIA CON EMODIALISI IN ELEZIONE E IN EMERGENZA</t>
+  </si>
+  <si>
+    <t>BSMP1310</t>
+  </si>
+  <si>
+    <t>RIABILITAZIONE SPECIALISTICA</t>
+  </si>
+  <si>
+    <t>DIP006</t>
+  </si>
+  <si>
+    <t>Dipartimento di chirurgia generale e della salute della donna</t>
+  </si>
+  <si>
+    <t>BSCS1405</t>
+  </si>
+  <si>
+    <t>CHIRURGIA DELLA TIROIDE E PARATIROIDI UOSD</t>
+  </si>
+  <si>
+    <t>BSTR0902</t>
+  </si>
+  <si>
+    <t>CHIRURGIA EPATOBILIARE E TRAPIANTO DI FEGATO</t>
+  </si>
+  <si>
+    <t>BSCS0710</t>
+  </si>
+  <si>
+    <t>CHIRURGIA GEN. AD ALTA SPEC. GASTROENTEROLOGICA</t>
+  </si>
+  <si>
+    <t>BSCS1600</t>
+  </si>
+  <si>
+    <t>CHIRURGIA GEN. AD ALTA SPEC. PANCREATICA</t>
+  </si>
+  <si>
+    <t>BSCS1600C</t>
+  </si>
+  <si>
+    <t>CHIRURGIA GEN. AD ALTA SPEC. PANCREATICA C.O.</t>
+  </si>
+  <si>
+    <t>BSCS0600</t>
+  </si>
+  <si>
+    <t>CHIRURGIA GEN. IND. ONCOLOGICO MIN. INV.ALTA SPEC. ESOFAGO-GASTRICA</t>
+  </si>
+  <si>
+    <t>BSCS1403</t>
+  </si>
+  <si>
+    <t>CHIRURGIA METABOLICA E DEI GRANDI OBESI UOSD</t>
+  </si>
+  <si>
+    <t>BSCS1402</t>
+  </si>
+  <si>
+    <t>CHIRURGIA SENOLOGICA</t>
+  </si>
+  <si>
+    <t>BSCP3500C</t>
+  </si>
+  <si>
+    <t>OSTETRICIA E GINECOLOGIA C.O.</t>
+  </si>
+  <si>
+    <t>BSCP3500</t>
+  </si>
+  <si>
+    <t>OSTETRICIA E GINECOLOGIA P.S. OSTETRICIA</t>
+  </si>
+  <si>
+    <t>BSCP3500-1</t>
+  </si>
+  <si>
+    <t>OSTETRICIA E GINECOLOGIA REPARTO</t>
+  </si>
+  <si>
+    <t>BSCS1404</t>
+  </si>
+  <si>
+    <t>WEEK E DAY SURGERY</t>
+  </si>
+  <si>
+    <t>DIP007</t>
+  </si>
+  <si>
+    <t>Dipartimento chirurgico polispecialistico</t>
+  </si>
+  <si>
+    <t>BSCP1407</t>
+  </si>
+  <si>
+    <t>ANDROLOGIA</t>
+  </si>
+  <si>
+    <t>BSEA0120</t>
+  </si>
+  <si>
+    <t>CENTRO GRANDI USTIONATI - CHIRURGIA PLASTICA RICOSTRUTTIVA</t>
+  </si>
+  <si>
+    <t>BSEA0120C</t>
+  </si>
+  <si>
+    <t>CENTRO GRANDI USTIONATI - CHIRURGIA PLASTICA RICOSTRUTTIVA C.O.</t>
+  </si>
+  <si>
+    <t>BSCS2230</t>
+  </si>
+  <si>
+    <t>CHIRURGIA MAXILLO FACCIALE</t>
+  </si>
+  <si>
+    <t>BSCS2230C</t>
+  </si>
+  <si>
+    <t>CHIRURGIA MAXILLO FACCIALE C.O.</t>
+  </si>
+  <si>
+    <t>BSCS0903</t>
+  </si>
+  <si>
+    <t>CHIRURGIA VASCOLARE ED ENDOVASCOLARE</t>
+  </si>
+  <si>
+    <t>BSCS0903C</t>
+  </si>
+  <si>
+    <t>CHIRURGIA VASCOLARE ED ENDOVASCOLARE C.O.</t>
+  </si>
+  <si>
+    <t>BSCP1404</t>
+  </si>
+  <si>
+    <t>MACULOPATIA E PATOLOGIA VITREO-RETINICA</t>
+  </si>
+  <si>
+    <t>BSMP30207</t>
+  </si>
+  <si>
+    <t>NEFROLOGIA CON EMODIALISI IN ELEZIONE E IN EMERGENZA DIALISI</t>
+  </si>
+  <si>
+    <t>BSCP1810</t>
+  </si>
+  <si>
+    <t>OCULISTICA</t>
+  </si>
+  <si>
+    <t>BSCP1810C</t>
+  </si>
+  <si>
+    <t>OCULISTICA C.O.</t>
+  </si>
+  <si>
+    <t>BSCS0510</t>
+  </si>
+  <si>
+    <t>ODONTOSTOMATOLOGIA</t>
+  </si>
+  <si>
+    <t>BSCP2400</t>
+  </si>
+  <si>
+    <t>ORTOPEDIA 1</t>
+  </si>
+  <si>
+    <t>BSCP2400C</t>
+  </si>
+  <si>
+    <t>ORTOPEDIA 1 C.O.</t>
+  </si>
+  <si>
+    <t>BSCP0208</t>
+  </si>
+  <si>
+    <t>ORTOPEDIA 2</t>
+  </si>
+  <si>
+    <t>BSCP0208C</t>
+  </si>
+  <si>
+    <t>ORTOPEDIA 2 C.O.</t>
+  </si>
+  <si>
+    <t>BSCP1800</t>
+  </si>
+  <si>
+    <t>OTORINOLARINGOIATRIA</t>
+  </si>
+  <si>
+    <t>BSCP1800C</t>
+  </si>
+  <si>
+    <t>OTORINOLARINGOIATRIA C.O.</t>
+  </si>
+  <si>
+    <t>BSEA28105</t>
+  </si>
+  <si>
+    <t>TERAPIA INTENSIVA NEONATALE NIDO</t>
+  </si>
+  <si>
+    <t>BSCP1500</t>
+  </si>
+  <si>
+    <t>UROLOGIA</t>
+  </si>
+  <si>
+    <t>BSCP1500C</t>
+  </si>
+  <si>
+    <t>UROLOGIA C.O.</t>
+  </si>
+  <si>
+    <t>DIP008</t>
+  </si>
+  <si>
+    <t>Dipartimento di anestesia e rianimazione</t>
+  </si>
+  <si>
+    <t>BSCS10105</t>
+  </si>
+  <si>
+    <t>CAMERA IPERBARICA (TIPO)</t>
+  </si>
+  <si>
+    <t>BSEA22804</t>
+  </si>
+  <si>
+    <t>CENTRO ANTIVELENI R.O.</t>
+  </si>
+  <si>
+    <t>BSCS1600CO-1</t>
+  </si>
+  <si>
+    <t>COMPLESSO OPERATORIO PAD. A</t>
+  </si>
+  <si>
+    <t>BSCS1600CO</t>
+  </si>
+  <si>
+    <t>COMPLESSO OPERATORIO PAD. H</t>
+  </si>
+  <si>
+    <t>BSEA2210</t>
+  </si>
+  <si>
+    <t>RIANIMAZIONE DEA</t>
+  </si>
+  <si>
+    <t>BSOP2214</t>
+  </si>
+  <si>
+    <t>SERVIZIO DI TERAPIA DEL DOLORE UOSD</t>
+  </si>
+  <si>
+    <t>BSCS1010-1</t>
+  </si>
+  <si>
+    <t>TEAM ACCESSI VASCOLARI</t>
+  </si>
+  <si>
+    <t>BSTR2213</t>
+  </si>
+  <si>
+    <t>TERAPIA INTENSIVA FEGATO</t>
+  </si>
+  <si>
+    <t>BSEA2280</t>
+  </si>
+  <si>
+    <t>TERAPIA INTENSIVA GRANDI USTIONI</t>
+  </si>
+  <si>
+    <t>BSEA2810</t>
+  </si>
+  <si>
+    <t>TERAPIA INTENSIVA NEONATALE E NEONATOLOGIA</t>
+  </si>
+  <si>
+    <t>BSCS1010</t>
+  </si>
+  <si>
+    <t>TERAPIA INTENSIVA POST OPERATORIA</t>
+  </si>
+  <si>
+    <t>BSTR2213C</t>
+  </si>
+  <si>
+    <t>TERAPIA INTENSIVA TRAPIANTI C.O.</t>
+  </si>
+  <si>
+    <t>DIP009</t>
+  </si>
+  <si>
+    <t>Dipartimento delle tecnologie avanzate diagnostico terapeutiche e dei servizi sanitari</t>
+  </si>
+  <si>
+    <t>BSTA4600</t>
+  </si>
+  <si>
+    <t>ANATOMIA PATOLOGICA</t>
+  </si>
+  <si>
+    <t>BSTA1003</t>
+  </si>
+  <si>
+    <t>DIAGNOSTICA SENOLOGICA UOSD</t>
+  </si>
+  <si>
+    <t>BSTA1002</t>
+  </si>
+  <si>
+    <t>FISICA SANITARIA UOSD</t>
+  </si>
+  <si>
+    <t>BSTA4810</t>
+  </si>
+  <si>
+    <t>GENETICA MEDICA E DI LABORATORIO</t>
+  </si>
+  <si>
+    <t>BSTA4111</t>
+  </si>
+  <si>
+    <t>MEDICINA NUCLEARE</t>
+  </si>
+  <si>
+    <t>BSTA4100</t>
+  </si>
+  <si>
+    <t>NEURORADIOLOGIA</t>
+  </si>
+  <si>
+    <t>BSTA5000</t>
+  </si>
+  <si>
+    <t>PATOLOGIA CLINICA</t>
+  </si>
+  <si>
+    <t>BSTA4330</t>
+  </si>
+  <si>
+    <t>RADIOLOGIA VASCOLARE ED INTERVENTISTICA</t>
+  </si>
+  <si>
+    <t>BSTA4010</t>
+  </si>
+  <si>
+    <t>SERVIZIO DI IMMUNOEMATOLOGIA E MEDICINA TRASFUSIONALE</t>
+  </si>
+  <si>
+    <t>DIP010</t>
+  </si>
+  <si>
+    <t>Dipartimento servizi strategici di area sanitaria</t>
+  </si>
+  <si>
+    <t>BSEA14081</t>
+  </si>
+  <si>
+    <t>COORDINAMENTO LOCALE OSPEALIERO PER IL PROCUREMENT DI ORGANI E TESSUTI (COP)</t>
+  </si>
+  <si>
+    <t>BSU7200</t>
+  </si>
+  <si>
+    <t>APPROPRIATEZZA ED EPIDEMIOLOGIA VALUTATIVA</t>
+  </si>
+  <si>
+    <t>BSU9208</t>
+  </si>
+  <si>
+    <t>ATTIVITA' IN LIBERA PROFESSIONE INTRAMOENIA UOSD</t>
+  </si>
+  <si>
+    <t>BSU90911</t>
+  </si>
+  <si>
+    <t>CENTRO UNICO DI PRENOTAZIONE CUP</t>
+  </si>
+  <si>
+    <t>BSU9096</t>
+  </si>
+  <si>
+    <t>DIREZIONE INFERMIERISTICA TECNICA E RIABILITATIVA</t>
+  </si>
+  <si>
+    <t>BSA9090-1</t>
+  </si>
+  <si>
+    <t>DIREZIONE SANITARIA - UFFICIO CARTELLE CLINICHE</t>
+  </si>
+  <si>
+    <t>BSA9090</t>
+  </si>
+  <si>
+    <t>DIREZIONE SANITARIA AZIENDALE</t>
+  </si>
+  <si>
+    <t>BSTA4800-1</t>
+  </si>
+  <si>
+    <t>FARMACIA</t>
+  </si>
+  <si>
+    <t>BSTA4800</t>
+  </si>
+  <si>
+    <t>FARMACIA UMACA</t>
+  </si>
+  <si>
+    <t>BSU4700-1</t>
+  </si>
+  <si>
+    <t>FORMAZIONE, RICERCA E COOPERAZIONE INTERN. - POLO DIDATTICO FISIOTERAPIA</t>
+  </si>
+  <si>
+    <t>BSU4700-2</t>
+  </si>
+  <si>
+    <t>FORMAZIONE, RICERCA E COOPERAZIONE INTERN. - POLO DIDATTICO INFERMIERISTICO</t>
+  </si>
+  <si>
+    <t>BSU4700-4</t>
+  </si>
+  <si>
+    <t>FORMAZIONE, RICERCA E COOPERAZIONE INTERN. - POLO DIDATTICO TECN. DI LABOR.</t>
+  </si>
+  <si>
+    <t>BSU4700-3</t>
+  </si>
+  <si>
+    <t>FORMAZIONE, RICERCA E COOPERAZIONE INTERN. - POLO DIDATTICO TECN. DI RADIOLOGIA</t>
+  </si>
+  <si>
+    <t>BSU4700</t>
+  </si>
+  <si>
+    <t>FORMAZIONE, RICERCA E COOPERAZIONE INTERNAZIONALE</t>
+  </si>
+  <si>
+    <t>BSU1409</t>
+  </si>
+  <si>
+    <t>GESTIONE SERVIZI DI SUPPORTO ALLA DIR. SAN. E DEI POSTI LETTO</t>
+  </si>
+  <si>
+    <t>BSU1409-7</t>
+  </si>
+  <si>
+    <t>GSSS - AUTOPARCO</t>
+  </si>
+  <si>
+    <t>BSU1409-4</t>
+  </si>
+  <si>
+    <t>GSSS - CELLA MORTUARIA</t>
+  </si>
+  <si>
+    <t>BSU1409-6</t>
+  </si>
+  <si>
+    <t>GSSS - NUCLEO SORV. SANITARIA</t>
+  </si>
+  <si>
+    <t>BSU1409-1</t>
+  </si>
+  <si>
+    <t>GSSS - POLIAMBULATORIO</t>
+  </si>
+  <si>
+    <t>BSU1409-5</t>
+  </si>
+  <si>
+    <t>GSSS - POLO DEA</t>
+  </si>
+  <si>
+    <t>BSU1409-3</t>
+  </si>
+  <si>
+    <t>GSSS - SERVIZIO SOCIALE</t>
+  </si>
+  <si>
+    <t>BSU1409-2</t>
+  </si>
+  <si>
+    <t>GSSS - UFFICIO CENTRALE</t>
+  </si>
+  <si>
+    <t>BSU1405</t>
+  </si>
+  <si>
+    <t>PREOSPEDALIZZAZIONE CENTRALIZZATA UOSD</t>
+  </si>
+  <si>
+    <t>BSU9095</t>
+  </si>
+  <si>
+    <t>PROGRAMMAZIONE E PIANIFICAZ. SANITARIA</t>
+  </si>
+  <si>
+    <t>BSU4500</t>
+  </si>
+  <si>
+    <t>RISK MANAGEMENT</t>
+  </si>
+  <si>
+    <t>DIP011</t>
+  </si>
+  <si>
+    <t>Dipartimento strutture di supporto alla direzione amministrativa</t>
+  </si>
+  <si>
+    <t>BAA9904</t>
+  </si>
+  <si>
+    <t>AFFARI GENERALI</t>
+  </si>
+  <si>
+    <t>BAA9912-1</t>
+  </si>
+  <si>
+    <t>COMUNICAZIONE E INNOVAZIONE - UFFICIO SICUREZZA E VIGILANZA</t>
+  </si>
+  <si>
+    <t>BAA9912</t>
+  </si>
+  <si>
+    <t>COMUNICAZIONE ED INNOVAZIONE</t>
+  </si>
+  <si>
+    <t>BAA9900</t>
+  </si>
+  <si>
+    <t>DIREZIONE AMMINISTRATIVA</t>
+  </si>
+  <si>
+    <t>BAA9905</t>
+  </si>
+  <si>
+    <t>GESTIONE ECONOMICA E FINANZIARIA</t>
+  </si>
+  <si>
+    <t>BAA9903</t>
+  </si>
+  <si>
+    <t>GESTIONE RISORSE UMANE</t>
+  </si>
+  <si>
+    <t>BAA9908</t>
+  </si>
+  <si>
+    <t>PIANIFICAZIONE E CONTROLLO DI GESTIONE</t>
+  </si>
+  <si>
+    <t>BAA9902</t>
+  </si>
+  <si>
+    <t>UFFICIO LEGALE E AVVOCATURA (ULA)</t>
+  </si>
+  <si>
+    <t>DIP012</t>
+  </si>
+  <si>
+    <t>Dipartimento strutture di supporto alla direzione generale</t>
+  </si>
+  <si>
+    <t>BAA9001</t>
+  </si>
+  <si>
+    <t>SEGRETARIATO GENERALE</t>
+  </si>
+  <si>
+    <t>BAA9911</t>
+  </si>
+  <si>
+    <t>SERV.PREVENZ.E PROTEZ.SICUR.ANTIINCENDIO</t>
+  </si>
+  <si>
+    <t>BAA9003</t>
+  </si>
+  <si>
+    <t>SERVIZIO ISPETTIVO</t>
   </si>
 </sst>
 </file>
@@ -137,8 +1031,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DipartimentiUOC" displayName="DipartimentiUOC" ref="A1:H3" headerRowCount="1">
-  <autoFilter ref="A1:H3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DipartimentiUOC" displayName="DipartimentiUOC" ref="A1:H152" headerRowCount="1">
+  <autoFilter ref="A1:H152"/>
   <tableColumns count="8">
     <tableColumn id="1" name="UOC Code"/>
     <tableColumn id="2" name="Description"/>
@@ -470,11 +1364,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.6114501953125" customWidth="1"/>
-    <col min="2" max="2" width="18.4405975341797" customWidth="1"/>
+    <col min="1" max="1" width="14.4291582107544" customWidth="1"/>
+    <col min="2" max="2" width="82.1693649291992" customWidth="1"/>
     <col min="3" max="3" width="20.6862239837646" customWidth="1"/>
     <col min="4" max="4" width="18.9309253692627" customWidth="1"/>
     <col min="5" max="5" width="18.4429225921631" customWidth="1"/>
@@ -526,7 +1420,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="0">
-        <v>10000</v>
+        <v>53228</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>12</v>
@@ -552,12 +1446,3886 @@
         <v>10</v>
       </c>
       <c r="F3" s="0">
-        <v>10001</v>
+        <v>78487</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="0">
+        <v>78473</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="0">
+        <v>78830</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="0">
+        <v>78487</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="0">
+        <v>78374</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="0">
+        <v>78392</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="0">
+        <v>31360</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="0">
+        <v>31360</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="0">
+        <v>31216</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="0">
+        <v>78392</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="0">
+        <v>78392</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="0">
+        <v>75344</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="0">
+        <v>79179</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="0">
+        <v>78392</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="0">
+        <v>72136</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="0">
+        <v>78961</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="0">
+        <v>72136</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="0">
+        <v>34295</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="0">
+        <v>30235</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="0">
+        <v>72136</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="0">
+        <v>78851</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="0">
+        <v>72172</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="0">
+        <v>70656</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="0">
+        <v>76351</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="0">
+        <v>70656</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="0">
+        <v>71845</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="0">
+        <v>36999</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="0">
+        <v>36999</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="0">
+        <v>75405</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="0">
+        <v>75405</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="0">
+        <v>75291</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="0">
+        <v>78851</v>
+      </c>
+      <c r="G34" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="0">
+        <v>31997</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="0">
+        <v>75420</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="0">
+        <v>72352</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="0">
+        <v>34809</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="0">
+        <v>37670</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="0">
+        <v>33144</v>
+      </c>
+      <c r="G40" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="0">
+        <v>70499</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="0">
+        <v>70499</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="0">
+        <v>70499</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="0">
+        <v>32349</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="0">
+        <v>34395</v>
+      </c>
+      <c r="G45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="0">
+        <v>34395</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="0">
+        <v>34395</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="0">
+        <v>71427</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="0">
+        <v>71427</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="0">
+        <v>71427</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="0">
+        <v>29539</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="0">
+        <v>29539</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="0">
+        <v>29539</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="0">
+        <v>76873</v>
+      </c>
+      <c r="G54" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="0">
+        <v>31997</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="0">
+        <v>30313</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="0">
+        <v>34944</v>
+      </c>
+      <c r="G57" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="0">
+        <v>76475</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="0">
+        <v>30313</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="0">
+        <v>35775</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="0">
+        <v>35775</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="0">
+        <v>78555</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="0">
+        <v>35167</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" s="0">
+        <v>38378</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" s="0">
+        <v>79508</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="0">
+        <v>79508</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="0">
+        <v>79508</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="0">
+        <v>72329</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="0">
+        <v>33601</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="0">
+        <v>31294</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="0">
+        <v>70466</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="0">
+        <v>70466</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="0">
+        <v>79539</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="0">
+        <v>79539</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" s="0">
+        <v>79123</v>
+      </c>
+      <c r="G75" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="0">
+        <v>79123</v>
+      </c>
+      <c r="G76" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" s="0">
+        <v>70555</v>
+      </c>
+      <c r="G77" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="0">
+        <v>76873</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F79" s="0">
+        <v>32815</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H79" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="0">
+        <v>32815</v>
+      </c>
+      <c r="G80" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H80" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="0">
+        <v>33479</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" s="0">
+        <v>34760</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="0">
+        <v>34760</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="0">
+        <v>71804</v>
+      </c>
+      <c r="G84" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H84" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="0">
+        <v>71804</v>
+      </c>
+      <c r="G85" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H85" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="0">
+        <v>75584</v>
+      </c>
+      <c r="G86" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H86" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="0">
+        <v>75584</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H87" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="0">
+        <v>76311</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="0">
+        <v>33601</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H89" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="0">
+        <v>33601</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H90" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="0">
+        <v>38611</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="0">
+        <v>75373</v>
+      </c>
+      <c r="G92" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="0">
+        <v>38611</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H93" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="0">
+        <v>75373</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="0">
+        <v>75373</v>
+      </c>
+      <c r="G95" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H95" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="0">
+        <v>70405</v>
+      </c>
+      <c r="G96" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" s="0">
+        <v>78857</v>
+      </c>
+      <c r="G97" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" s="0">
+        <v>75373</v>
+      </c>
+      <c r="G98" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="0">
+        <v>72243</v>
+      </c>
+      <c r="G99" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H99" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="0">
+        <v>38611</v>
+      </c>
+      <c r="G100" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="0">
+        <v>76311</v>
+      </c>
+      <c r="G101" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H101" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" s="0">
+        <v>75373</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" s="0">
+        <v>72243</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H103" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" s="0">
+        <v>35946</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H104" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="0">
+        <v>30691</v>
+      </c>
+      <c r="G105" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="0">
+        <v>35716</v>
+      </c>
+      <c r="G106" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="0">
+        <v>75578</v>
+      </c>
+      <c r="G107" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H107" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E108" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" s="0">
+        <v>78706</v>
+      </c>
+      <c r="G108" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H108" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" s="0">
+        <v>76789</v>
+      </c>
+      <c r="G109" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H109" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="0">
+        <v>35946</v>
+      </c>
+      <c r="G110" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H110" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="0">
+        <v>33778</v>
+      </c>
+      <c r="G111" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H111" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" s="0">
+        <v>36135</v>
+      </c>
+      <c r="G112" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H112" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" s="0">
+        <v>77322</v>
+      </c>
+      <c r="G113" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H113" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" s="0">
+        <v>38611</v>
+      </c>
+      <c r="G114" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H114" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="0">
+        <v>30648</v>
+      </c>
+      <c r="G115" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H115" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="0">
+        <v>35164</v>
+      </c>
+      <c r="G116" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H116" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" s="0">
+        <v>78261</v>
+      </c>
+      <c r="G117" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H117" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="0">
+        <v>78261</v>
+      </c>
+      <c r="G118" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H118" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="0">
+        <v>75405</v>
+      </c>
+      <c r="G119" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H119" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="C120" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="0">
+        <v>53265</v>
+      </c>
+      <c r="G120" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H120" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="0">
+        <v>53265</v>
+      </c>
+      <c r="G121" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H121" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C122" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="0">
+        <v>76338</v>
+      </c>
+      <c r="G122" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H122" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="C123" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="0">
+        <v>76338</v>
+      </c>
+      <c r="G123" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H123" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C124" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="0">
+        <v>75296</v>
+      </c>
+      <c r="G124" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H124" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C125" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="0">
+        <v>75296</v>
+      </c>
+      <c r="G125" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H125" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="C126" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="0">
+        <v>75296</v>
+      </c>
+      <c r="G126" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H126" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="C127" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F127" s="0">
+        <v>75296</v>
+      </c>
+      <c r="G127" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H127" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" s="0">
+        <v>21396</v>
+      </c>
+      <c r="G128" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H128" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="C129" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G129" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H129" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="C130" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E130" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G130" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H130" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F131" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G131" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H131" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="C132" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E132" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F132" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G132" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H132" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="C133" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G133" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H133" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G134" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H134" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F135" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G135" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H135" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D136" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" s="0">
+        <v>79509</v>
+      </c>
+      <c r="G136" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H136" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D137" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" s="0">
+        <v>72328</v>
+      </c>
+      <c r="G137" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H137" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D138" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="0">
+        <v>75206</v>
+      </c>
+      <c r="G138" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H138" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139" s="0">
+        <v>53265</v>
+      </c>
+      <c r="G139" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H139" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="0">
+        <v>53228</v>
+      </c>
+      <c r="G140" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H140" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F141" s="0">
+        <v>75256</v>
+      </c>
+      <c r="G141" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H141" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F142" s="0">
+        <v>78474</v>
+      </c>
+      <c r="G142" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H142" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F143" s="0">
+        <v>78474</v>
+      </c>
+      <c r="G143" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H143" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" s="0">
+        <v>53228</v>
+      </c>
+      <c r="G144" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H144" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="C145" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F145" s="0">
+        <v>76025</v>
+      </c>
+      <c r="G145" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H145" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" s="0">
+        <v>76164</v>
+      </c>
+      <c r="G146" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H146" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" s="0">
+        <v>76716</v>
+      </c>
+      <c r="G147" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H147" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" s="0">
+        <v>78349</v>
+      </c>
+      <c r="G148" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H148" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" s="0">
+        <v>53228</v>
+      </c>
+      <c r="G149" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H149" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="C150" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" s="0">
+        <v>53228</v>
+      </c>
+      <c r="G150" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H150" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D151" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" s="0">
+        <v>76453</v>
+      </c>
+      <c r="G151" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H151" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D152" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" s="0">
+        <v>78349</v>
+      </c>
+      <c r="G152" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" s="0" t="s">
         <v>13</v>
       </c>
     </row>

--- a/script/templates/IMPORT_DIPARTIMENTO_E_UOC.xlsx
+++ b/script/templates/IMPORT_DIPARTIMENTO_E_UOC.xlsx
@@ -2694,7 +2694,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="0">
-        <v>29539</v>
+        <v>38426</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>12</v>
@@ -2720,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="0">
-        <v>29539</v>
+        <v>38426</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>12</v>
@@ -2746,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="0">
-        <v>29539</v>
+        <v>38426</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>12</v>
